--- a/src/test/resources/ImportTemplate/Checksum.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F5977A4-28E0-4B85-85BE-88B623CF221B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA5847C-F01D-4BC1-9939-800533AD1024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 FROM public.customer;</t>
   </si>
   <si>
-    <t>Checksum_ImportSQL-DB-PostgreSQL--Customer</t>
+    <t>Checksum_ImportSQL DB PostgreSQL Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Checksum.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA5847C-F01D-4BC1-9939-800533AD1024}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E70C486-C65E-4BC4-BFC5-3AE35567A55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,11 +36,10 @@
     <t>targetSql</t>
   </si>
   <si>
-    <t>select DISTINCT jobcode
-FROM public.customer;</t>
+    <t>Checksum_ImportSQL DB PostgreSQL Customer</t>
   </si>
   <si>
-    <t>Checksum_ImportSQL DB PostgreSQL Customer</t>
+    <t>select Count (*) FROM public.customer;</t>
   </si>
 </sst>
 </file>
@@ -90,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -99,6 +98,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -398,18 +400,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/test/resources/ImportTemplate/Checksum.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E70C486-C65E-4BC4-BFC5-3AE35567A55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBFCEA3-57DF-4920-9225-DB2E6CDF26F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,10 @@
     <t>targetSql</t>
   </si>
   <si>
-    <t>Checksum_ImportSQL DB PostgreSQL Customer</t>
+    <t>select Count (*) FROM public.customer;</t>
   </si>
   <si>
-    <t>select Count (*) FROM public.customer;</t>
+    <t>Checksum_ImportSQL--DB-PostgreSQL_Customer</t>
   </si>
 </sst>
 </file>
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -98,9 +98,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -400,15 +397,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>4</v>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ImportTemplate/Checksum.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBFCEA3-57DF-4920-9225-DB2E6CDF26F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B29178-92F4-4337-8B2D-2624824335DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
     <t>select Count (*) FROM public.customer;</t>
   </si>
   <si>
-    <t>Checksum_ImportSQL--DB-PostgreSQL_Customer</t>
+    <t>Checksum_ImportSQL__DB_PostgreSQL_Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Checksum.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B29178-92F4-4337-8B2D-2624824335DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEDBF14-A678-433A-A838-DB5B7840C8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,10 +36,10 @@
     <t>targetSql</t>
   </si>
   <si>
-    <t>select Count (*) FROM public.customer;</t>
+    <t>Checksum_ImportSQL__DB_PostgreSQL_Customer</t>
   </si>
   <si>
-    <t>Checksum_ImportSQL__DB_PostgreSQL_Customer</t>
+    <t>select Count (*) FROM icedq.customer;</t>
   </si>
 </sst>
 </file>
@@ -399,13 +399,13 @@
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="C2" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ImportTemplate/Checksum.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEDBF14-A678-433A-A838-DB5B7840C8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9567B0A7-C1E7-4AA1-8839-0474D17698BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>ruleName</t>
   </si>
@@ -39,7 +39,10 @@
     <t>Checksum_ImportSQL__DB_PostgreSQL_Customer</t>
   </si>
   <si>
-    <t>select Count (*) FROM icedq.customer;</t>
+    <t>select Count (*) AS SOURCE_COUNT FROM icedq.customer;</t>
+  </si>
+  <si>
+    <t>select Count (*) AS TARGET_COUNT FROM icedq.customer;</t>
   </si>
 </sst>
 </file>
@@ -383,7 +386,8 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="43.7109375" customWidth="1"/>
+    <col min="1" max="1" width="47.5703125" customWidth="1"/>
+    <col min="2" max="3" width="43.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -405,7 +409,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
